--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC24898B-1E6D-1541-87E5-D44411DA6000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDBFB8A-C814-8D44-9DB5-F659507AC4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38480" yWindow="500" windowWidth="33440" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>

--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDBFB8A-C814-8D44-9DB5-F659507AC4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5281CF16-B6FF-3C4B-A9D7-2117BA8FCEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38480" yWindow="500" windowWidth="33440" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>
